--- a/terraform/performance-test/result/output_data.xlsx
+++ b/terraform/performance-test/result/output_data.xlsx
@@ -495,31 +495,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>511.6605774886878</v>
+        <v>512.4635630252101</v>
       </c>
       <c r="D2" t="n">
-        <v>17.749</v>
+        <v>31.804</v>
       </c>
       <c r="E2" t="n">
-        <v>1003.548</v>
+        <v>991.285</v>
       </c>
       <c r="F2" t="n">
-        <v>206.914059800677</v>
+        <v>218.248061995994</v>
       </c>
       <c r="G2" t="n">
-        <v>515.8330000000001</v>
+        <v>524.927</v>
       </c>
       <c r="H2" t="n">
-        <v>663.0767499999999</v>
+        <v>673.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>784.1757</v>
+        <v>799.7208000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>850.0669999999999</v>
+        <v>852.5773</v>
       </c>
       <c r="K2" t="n">
-        <v>944.2961799999996</v>
+        <v>931.4819799999997</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>469.5237106347898</v>
+        <v>514.3469933719966</v>
       </c>
       <c r="D3" t="n">
-        <v>53.598</v>
+        <v>33.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1141.95</v>
+        <v>1016.867</v>
       </c>
       <c r="F3" t="n">
-        <v>207.656958978681</v>
+        <v>211.228880935155</v>
       </c>
       <c r="G3" t="n">
-        <v>468.763</v>
+        <v>516.096</v>
       </c>
       <c r="H3" t="n">
-        <v>607.381</v>
+        <v>667.5335</v>
       </c>
       <c r="I3" t="n">
-        <v>764.7765999999999</v>
+        <v>794.7548000000002</v>
       </c>
       <c r="J3" t="n">
-        <v>838.6953999999999</v>
+        <v>869.0073000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>923.8299199999998</v>
+        <v>973.4741800000002</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>509.4932857977791</v>
+        <v>543.3570279569892</v>
       </c>
       <c r="D4" t="n">
-        <v>51.858</v>
+        <v>44.138</v>
       </c>
       <c r="E4" t="n">
-        <v>989.217</v>
+        <v>1003.088</v>
       </c>
       <c r="F4" t="n">
-        <v>195.513268153223</v>
+        <v>213.831789963158</v>
       </c>
       <c r="G4" t="n">
-        <v>509.635</v>
+        <v>544.5605</v>
       </c>
       <c r="H4" t="n">
-        <v>643.8855</v>
+        <v>707.1955</v>
       </c>
       <c r="I4" t="n">
-        <v>768.655</v>
+        <v>828.9502</v>
       </c>
       <c r="J4" t="n">
-        <v>835.756</v>
+        <v>891.61595</v>
       </c>
       <c r="K4" t="n">
-        <v>936.9842000000001</v>
+        <v>959.0551100000001</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>572.1218892455859</v>
+        <v>524.9087838063439</v>
       </c>
       <c r="D5" t="n">
-        <v>50.61</v>
+        <v>69.56399999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>998.992</v>
+        <v>1266.107</v>
       </c>
       <c r="F5" t="n">
-        <v>190.68461606606</v>
+        <v>207.576054372617</v>
       </c>
       <c r="G5" t="n">
-        <v>571.6235</v>
+        <v>523.72</v>
       </c>
       <c r="H5" t="n">
-        <v>717.5587499999999</v>
+        <v>666.449</v>
       </c>
       <c r="I5" t="n">
-        <v>826.3944</v>
+        <v>809.4545000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>873.61675</v>
+        <v>871.49725</v>
       </c>
       <c r="K5" t="n">
-        <v>940.3729400000005</v>
+        <v>955.6616000000005</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>554.3936096291477</v>
+        <v>567.6929953488373</v>
       </c>
       <c r="D6" t="n">
-        <v>60.198</v>
+        <v>33.064</v>
       </c>
       <c r="E6" t="n">
-        <v>1008.36</v>
+        <v>1003.79</v>
       </c>
       <c r="F6" t="n">
-        <v>206.386527935978</v>
+        <v>195.760796276349</v>
       </c>
       <c r="G6" t="n">
-        <v>553.8345</v>
+        <v>570.0509999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>713.31125</v>
+        <v>709.7329999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>829.9512000000002</v>
+        <v>829.0631</v>
       </c>
       <c r="J6" t="n">
-        <v>888.1639499999999</v>
+        <v>885.8029499999998</v>
       </c>
       <c r="K6" t="n">
-        <v>961.3357199999999</v>
+        <v>958.0398599999999</v>
       </c>
     </row>
     <row r="7">
@@ -680,31 +680,31 @@
         <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>569.8942392255892</v>
+        <v>550.5027249273877</v>
       </c>
       <c r="D7" t="n">
-        <v>88.03100000000001</v>
+        <v>86.211</v>
       </c>
       <c r="E7" t="n">
-        <v>1390.569</v>
+        <v>1082.871</v>
       </c>
       <c r="F7" t="n">
-        <v>194.960510192412</v>
+        <v>188.832964734049</v>
       </c>
       <c r="G7" t="n">
-        <v>570.0160000000001</v>
+        <v>548.12</v>
       </c>
       <c r="H7" t="n">
-        <v>712.957</v>
+        <v>685.456</v>
       </c>
       <c r="I7" t="n">
-        <v>834.0262</v>
+        <v>802.6526</v>
       </c>
       <c r="J7" t="n">
-        <v>893.6451499999999</v>
+        <v>864.1347999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>971.5587999999998</v>
+        <v>955.5583599999999</v>
       </c>
     </row>
   </sheetData>
